--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -181,6 +181,18 @@
   </si>
   <si>
     <t>Leukocytes [#/volume] in Blood</t>
+  </si>
+  <si>
+    <t>789-8</t>
+  </si>
+  <si>
+    <t>Erythrocytes [#/volume] in Blood</t>
+  </si>
+  <si>
+    <t>787-2</t>
+  </si>
+  <si>
+    <t>MCV [Entitic volume] by Automated count</t>
   </si>
   <si>
     <t>89015-2</t>
@@ -500,7 +512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -677,18 +689,34 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>1558-6</t>
   </si>
   <si>
-    <t>Fasting Glucose [Mass/volume] in Serum or Plasma</t>
+    <t>Fasting glucose [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>2093-3</t>
@@ -150,7 +150,7 @@
     <t>2089-1</t>
   </si>
   <si>
-    <t>Cholesterol in LDL [Mass/volume] in Serum or Plasma by Direct assay</t>
+    <t>Cholesterol in LDL [Mass/volume] in Serum or Plasma</t>
   </si>
   <si>
     <t>1742-6</t>
@@ -168,7 +168,7 @@
     <t>5804-0</t>
   </si>
   <si>
-    <t>Protein [Presence] in Urine by Test strip</t>
+    <t>Protein [Mass/volume] in Urine by Test strip</t>
   </si>
   <si>
     <t>718-7</t>
@@ -198,7 +198,7 @@
     <t>89015-2</t>
   </si>
   <si>
-    <t>Pure tone threshold audiometry panel</t>
+    <t>Pure tone air conduction threshold audiometry panel</t>
   </si>
   <si>
     <t>5671-3</t>
@@ -216,19 +216,19 @@
     <t>19876-2</t>
   </si>
   <si>
-    <t>Forced vital capacity [Volume] in Airways by Spirometry</t>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry --pre bronchodilation</t>
   </si>
   <si>
     <t>20150-9</t>
   </si>
   <si>
-    <t>Forced expiratory volume in 1 second [Volume] in Airways by Spirometry</t>
+    <t>FEV1</t>
   </si>
   <si>
     <t>19926-5</t>
   </si>
   <si>
-    <t>Forced expiratory volume in 1 second/Forced vital capacity [Volume Ratio] in Airways by Spirometry</t>
+    <t>FEV1/FVC</t>
   </si>
   <si>
     <t>36643-5</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -213,10 +213,10 @@
     <t>Lead [Mass/volume] in Specimen</t>
   </si>
   <si>
-    <t>19876-2</t>
-  </si>
-  <si>
-    <t>Forced vital capacity [Volume] Respiratory system by Spirometry --pre bronchodilation</t>
+    <t>19868-9</t>
+  </si>
+  <si>
+    <t>Forced vital capacity [Volume] Respiratory system by Spirometry</t>
   </si>
   <si>
     <t>20150-9</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -201,10 +201,10 @@
     <t>Pure tone air conduction threshold audiometry panel</t>
   </si>
   <si>
-    <t>5671-3</t>
-  </si>
-  <si>
-    <t>Lead [Mass/volume] in Blood</t>
+    <t>77307-7</t>
+  </si>
+  <si>
+    <t>Lead [Mass/volume] in Venous blood</t>
   </si>
   <si>
     <t>23749-5</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -180,19 +180,19 @@
     <t>6690-2</t>
   </si>
   <si>
-    <t>Leukocytes [#/volume] in Blood</t>
+    <t>Leukocytes [#/volume] in Blood by Automated count</t>
   </si>
   <si>
     <t>789-8</t>
   </si>
   <si>
-    <t>Erythrocytes [#/volume] in Blood</t>
+    <t>Erythrocytes [#/volume] in Blood by Automated count</t>
   </si>
   <si>
     <t>787-2</t>
   </si>
   <si>
-    <t>MCV [Entitic volume] by Automated count</t>
+    <t>MCV [Entitic mean volume] in Red Blood Cells by Automated count</t>
   </si>
   <si>
     <t>89015-2</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,10 +117,10 @@
     <t>Body weight</t>
   </si>
   <si>
-    <t>55284-4</t>
-  </si>
-  <si>
-    <t>Blood pressure systolic and diastolic</t>
+    <t>85354-9</t>
+  </si>
+  <si>
+    <t>Blood pressure panel with all children optional</t>
   </si>
   <si>
     <t>1558-6</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>第一期法定必驗之勞工健康檢查項目草案子集，涵蓋附表九一般必驗生理量測與實驗室項目，以及噪音／鉛／粉塵三模組之核心必驗代碼。此為初版草案，範疇待附表九/十逐項法規盤點確認後修訂。</t>
+    <t>【依據：勞工健康保護規則附表】第一期法定必驗之勞工健康檢查項目草案子集，涵蓋附表九一般必驗生理量測與實驗室項目，以及噪音／鉛／粉塵三模組之核心必驗代碼。此為初版草案，範疇待附表九/十逐項法規盤點確認後修訂。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-OccHealthCheck-Required.xlsx
+++ b/ValueSet-VS-OccHealthCheck-Required.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
